--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_ILL.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_ILL.xlsx
@@ -933,7 +933,11 @@
           <t>ILL_D._WOODSON</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322870</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>D. Woodson</t>
@@ -3249,7 +3253,11 @@
           <t>ILL_D._WOODSON</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322870</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>D. Woodson</t>
@@ -4597,7 +4605,11 @@
           <t>ILL_D._WOODSON</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322870</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>D. Woodson</t>
@@ -6429,7 +6441,11 @@
           <t>ILL_D._WOODSON</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322870</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>D. Woodson</t>
@@ -8276,7 +8292,11 @@
           <t>ILL_D._WOODSON</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322870</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>D. Woodson</t>
@@ -8566,7 +8586,11 @@
           <t>ILL_D._WOODSON</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>322870</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>D. Woodson</t>
@@ -9700,7 +9724,11 @@
           <t>ILL_D._WOODSON</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322870</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>D. Woodson</t>
@@ -10382,7 +10410,11 @@
           <t>ILL_D._WOODSON</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>322870</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>D. Woodson</t>
